--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,120 @@
         <is>
           <t>Variacion (%)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-12 20:32:39</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31866425.5</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31871088.6</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4663.10000000149</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.01463326974028352</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-12 20:32:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>33506846.9</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33582899.3</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>76052.39999999851</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2269756991070339</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-12 20:32:39</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>35255452.9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>35301585.1</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>46132.20000000298</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1308512476945176</v>
       </c>
     </row>
   </sheetData>
@@ -471,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +609,18 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-12 20:32:40</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cambios detectados (3)</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,6 +571,120 @@
         <v>46132.20000000298</v>
       </c>
       <c r="H4" t="n">
+        <v>0.1308512476945176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:20:26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31866425.5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>31871088.6</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4663.10000000149</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.01463326974028352</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:20:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>33506846.9</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33582899.3</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>76052.39999999851</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2269756991070339</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:20:26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>35255452.9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>35301585.1</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>46132.20000000298</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.1308512476945176</v>
       </c>
     </row>
@@ -585,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,6 +733,18 @@
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>Cambios detectados (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:20:27</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Cambios detectados (3)</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,147 @@
       </c>
       <c r="H7" t="n">
         <v>0.1308512476945176</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:24:29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>31866425.5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>31871088.6</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>4663.10000000149</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.01463326974028352</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:24:29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>33506846.9</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>33582899.3</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>76052.39999999851</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2269756991070339</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:24:29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>35255452.9</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>35301585.1</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>46132.20000000298</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1308512476945176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:24:29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nuevo dato publicado</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>35455860.9</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -699,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,6 +888,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Cambios detectados (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-15 18:24:30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cambios detectados (4)</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,18 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Cambios detectados (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:16:12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -910,6 +910,18 @@
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-21 19:05:51</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,18 @@
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:50:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,18 @@
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-23 21:06:06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,18 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-24 20:22:37</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,18 @@
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-25 21:03:17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,6 +970,18 @@
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-26 20:22:35</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,18 @@
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-27 17:44:35</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,18 @@
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-28 17:52:29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,18 @@
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-29 20:32:15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -840,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,18 @@
         </is>
       </c>
       <c r="B15" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-30 20:33:18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,6 +824,147 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>35455860.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-02 19:30:51</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>31866425.5</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>31871088.6</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>4663.10000000149</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01463326974028352</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-02 19:30:51</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>33506846.9</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>33582899.3</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>76052.39999999851</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2269756991070339</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-02 19:30:51</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>35255452.9</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>35301585.1</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>46132.20000000298</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1308512476945176</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-02 19:30:51</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nuevo dato publicado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>35455860.9</t>
         </is>
@@ -840,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1173,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-02 19:30:53</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cambios detectados (4)</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -965,6 +965,147 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>35455860.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-02 20:32:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>31866425.5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31871088.6</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>4663.10000000149</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01463326974028352</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-02 20:32:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>33506846.9</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>33582899.3</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>76052.39999999851</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2269756991070339</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-02 20:32:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>35255452.9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>35301585.1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>46132.20000000298</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1308512476945176</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-02 20:32:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nuevo dato publicado</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>35455860.9</t>
         </is>
@@ -981,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,6 +1324,18 @@
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Cambios detectados (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-02 20:32:03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>Cambios detectados (4)</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,6 +1338,18 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Cambios detectados (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-20 19:17:52</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,6 +1348,18 @@
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-21 15:40:12</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1360,6 +1360,18 @@
         </is>
       </c>
       <c r="B20" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-22 15:29:02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1372,18 @@
         </is>
       </c>
       <c r="B21" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-23 15:52:04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1384,6 +1384,18 @@
         </is>
       </c>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-24 15:22:12</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,18 @@
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-25 14:58:19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1408,18 @@
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-26 15:00:40</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,6 +1420,18 @@
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:13:13</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,6 +1432,18 @@
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:02:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1444,18 @@
         </is>
       </c>
       <c r="B27" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-29 15:47:33</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,6 +1456,18 @@
         </is>
       </c>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-30 15:48:32</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1468,18 @@
         </is>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:30:53</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,18 @@
         </is>
       </c>
       <c r="B30" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:29:25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,18 @@
         </is>
       </c>
       <c r="B31" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-22 14:16:04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,18 @@
         </is>
       </c>
       <c r="B32" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-23 14:18:16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,98 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>35455860.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:36:08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Corrección</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>35455860.9</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>35458611.7</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2750.80000000447</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.007758378812921365</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:36:08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2T</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nuevo dato publicado</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>37530380.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:36:08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6 meses</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nuevo dato publicado</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>36494496.0</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,6 +1610,18 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-24 14:36:10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cambios detectados (3)</t>
         </is>
       </c>
     </row>
@@ -1657,13 +1761,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35455860.9</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>35458611.7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>37530380.3</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>36494496.0</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,18 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>Cambios detectados (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-25 14:39:14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
         </is>
       </c>
     </row>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1632,6 +1632,18 @@
         </is>
       </c>
       <c r="B35" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-26 14:39:03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1644,6 +1644,18 @@
         </is>
       </c>
       <c r="B36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-27 23:30:27</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,6 +1656,18 @@
         </is>
       </c>
       <c r="B37" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-28 23:21:43</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1668,6 +1668,18 @@
         </is>
       </c>
       <c r="B38" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:28:15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>

--- a/monitoreo_pib.xlsx
+++ b/monitoreo_pib.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1680,18 @@
         </is>
       </c>
       <c r="B39" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:52:02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Sin cambios</t>
         </is>
